--- a/roubaix_donnees_graphiques.xlsx
+++ b/roubaix_donnees_graphiques.xlsx
@@ -5156,7 +5156,7 @@
         <v>80.2</v>
       </c>
       <c r="C5" t="n">
-        <v>82.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D5" t="n">
         <v>89.90000000000001</v>
